--- a/reports/pdf_rolling5_20260915.xlsx
+++ b/reports/pdf_rolling5_20260915.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 73억(1.6%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 10종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 37억(0.8%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 10종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1192,23 +1192,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-764586900</v>
+        <v>-1191564000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.25%→1.01%</t>
+          <t>6.52%→5.54%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>61→52</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1191564000</v>
+        <v>-764586900</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.52%→5.54%</t>
+          <t>1.25%→1.01%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>61→52</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,371억   ·   현금 86억(2.5%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,371억   ·   현금 43억(1.3%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1323,7 +1323,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,459억   ·   현금 80억(3.2%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,459억   ·   현금 40억(1.6%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1544,7 +1544,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,915억   ·   현금 34억(1.8%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,915억   ·   현금 17억(0.9%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1765,7 +1765,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 1억(0.4%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 6종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 2억(0.7%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 6종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -2146,7 +2146,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 9억(1.9%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 4억(0.9%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260915.xlsx
+++ b/reports/pdf_rolling5_20260915.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-08 ~ 2026-09-15  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-08 ~ 2026-09-15  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -1108,23 +1108,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-781136400</v>
+        <v>-764286000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.82%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1136,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-764286000</v>
+        <v>-781136400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.06%→0.82%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1220,23 +1220,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2130372000</v>
+        <v>-764586900</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.32%→2.60%</t>
+          <t>1.25%→1.01%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>61→52</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-764586900</v>
+        <v>-2130372000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.25%→1.01%</t>
+          <t>3.32%→2.60%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>61→52</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
@@ -1763,448 +1763,82 @@
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 2억(0.7%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 6종목  /  매도 7종목</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 4억(0.9%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>137</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>92639400</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>7.14%→7.47%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>2,843→2,980</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-106</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-34799800</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>2.99%→2.86%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>2,452→2,346</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>선익시스템</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>183183000</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>0.33%→1.01%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>19→58</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-62</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-103292000</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>5.63%→5.23%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>909→847</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>84766500</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>1.17%→1.48%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>100→127</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-37</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-116161500</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>4.17%→3.74%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>358→321</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>39130000</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>1.64%→1.78%</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>293→319</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-28028000</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>2.10%→1.99%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>262→249</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>48762000</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>2.66%→2.83%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>88→94</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-23940000</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>1.10%→1.01%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>111→102</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>대주전자재료</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>23212000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>1.70%→1.79%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>79→83</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-53949000</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>2.43%→2.23%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>85→78</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-63070000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>1.78%→1.54%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>38→33</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 4억(0.9%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
-      <c r="H55" s="20" t="n"/>
-      <c r="I55" s="20" t="n"/>
-      <c r="J55" s="20" t="n"/>
-      <c r="K55" s="20" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="20" t="n"/>
+      <c r="K46" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="17">
     <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A44:K44"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="G28:K28"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A2:K2"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A52:K52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260915.xlsx
+++ b/reports/pdf_rolling5_20260915.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-08 ~ 2026-09-15  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-08 ~ 2026-09-15  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1108,23 +1108,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-764286000</v>
+        <v>-781136400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.06%→0.82%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1136,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-781136400</v>
+        <v>-764286000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.82%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1220,23 +1220,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-764586900</v>
+        <v>-2130372000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.25%→1.01%</t>
+          <t>3.32%→2.60%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>61→52</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2130372000</v>
+        <v>-764586900</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.32%→2.60%</t>
+          <t>1.25%→1.01%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>61→52</t>
         </is>
       </c>
     </row>
@@ -1763,82 +1763,448 @@
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="20" t="n"/>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="20" t="n"/>
-      <c r="J41" s="20" t="n"/>
-      <c r="K41" s="20" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 1억(0.4%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 6종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>137</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>92639400</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>7.14%→7.47%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>2,843→2,980</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-106</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-34799800</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>2.99%→2.86%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>2,452→2,346</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>183183000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>0.33%→1.01%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>19→58</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-103292000</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>5.63%→5.23%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>909→847</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>84766500</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>1.17%→1.48%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>100→127</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-37</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-116161500</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>4.17%→3.74%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>358→321</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>39130000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→1.78%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>293→319</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-28028000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2.10%→1.99%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>262→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>48762000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>2.66%→2.83%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>88→94</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-23940000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>1.10%→1.01%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>111→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>23212000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>1.70%→1.79%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>79→83</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-53949000</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>2.43%→2.23%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>85→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-63070000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>1.78%→1.54%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>38→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 4억(0.9%)      오늘 2026-09-15  vs  5일전 2026-09-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="20" t="n"/>
-      <c r="J46" s="20" t="n"/>
-      <c r="K46" s="20" t="n"/>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
+      <c r="H55" s="20" t="n"/>
+      <c r="I55" s="20" t="n"/>
+      <c r="J55" s="20" t="n"/>
+      <c r="K55" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G28:K28"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A52:K52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260915.xlsx
+++ b/reports/pdf_rolling5_20260915.xlsx
@@ -1192,23 +1192,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1191564000</v>
+        <v>-764586900</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>6.52%→5.54%</t>
+          <t>1.25%→1.01%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>61→52</t>
         </is>
       </c>
     </row>
@@ -1220,23 +1220,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2130372000</v>
+        <v>-1191564000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.32%→2.60%</t>
+          <t>6.52%→5.54%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-764586900</v>
+        <v>-2130372000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.25%→1.01%</t>
+          <t>3.32%→2.60%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>61→52</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
